--- a/epiverse/data/Prostatic.xlsx
+++ b/epiverse/data/Prostatic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mark/Classes/Epi/Epiverse/epiverse/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC02D250-01CA-674E-B195-3CB9DED6B7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983C0499-B92C-0644-A65F-3A2294DCB369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="500" windowWidth="32360" windowHeight="20500" xr2:uid="{05CE7BC3-13E5-AD4F-9ECC-1ED45C6A6B43}"/>
+    <workbookView xWindow="17420" yWindow="500" windowWidth="16180" windowHeight="20500" xr2:uid="{05CE7BC3-13E5-AD4F-9ECC-1ED45C6A6B43}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="62">
   <si>
     <t>PID</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>BM</t>
-  </si>
-  <si>
-    <t>I</t>
   </si>
   <si>
     <t>MosFU</t>
@@ -641,25 +638,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
         <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
@@ -671,13 +668,13 @@
         <v>8</v>
       </c>
       <c r="N1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>22</v>
-      </c>
-      <c r="P1" t="s">
-        <v>23</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>9</v>
@@ -13783,7 +13780,7 @@
         <v>24650</v>
       </c>
       <c r="H203" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I203">
         <v>1</v>
@@ -14888,7 +14885,7 @@
         <v>24616</v>
       </c>
       <c r="H220" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I220">
         <v>1</v>
@@ -14985,8 +14982,8 @@
       <c r="R221">
         <v>6</v>
       </c>
-      <c r="S221" t="s">
-        <v>14</v>
+      <c r="S221">
+        <v>1</v>
       </c>
       <c r="T221">
         <v>7</v>
@@ -22558,7 +22555,7 @@
         <v>24929</v>
       </c>
       <c r="H338" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I338">
         <v>7</v>
@@ -24118,7 +24115,7 @@
         <v>25188</v>
       </c>
       <c r="H362" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I362">
         <v>2</v>
@@ -25483,7 +25480,7 @@
         <v>24688</v>
       </c>
       <c r="H383" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I383">
         <v>2</v>
@@ -29058,7 +29055,7 @@
         <v>24729</v>
       </c>
       <c r="H438" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I438">
         <v>2</v>
@@ -30502,8 +30499,8 @@
       <c r="L460">
         <v>0</v>
       </c>
-      <c r="M460" t="s">
-        <v>14</v>
+      <c r="M460">
+        <v>1</v>
       </c>
       <c r="N460">
         <v>15</v>
@@ -33606,13 +33603,13 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -33620,7 +33617,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -33628,7 +33625,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -33636,7 +33633,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -33644,10 +33641,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H5" s="1" t="str">
         <f>_xlfn.TEXTJOIN("; ", TRUE, I5:L5)</f>
@@ -33660,10 +33657,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>4</v>
@@ -33675,13 +33672,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -33690,24 +33687,24 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -33715,10 +33712,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="H10" s="1" t="str">
         <f>_xlfn.TEXTJOIN("; ", TRUE, I10:T10)</f>
@@ -33740,10 +33737,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -33761,10 +33758,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -33779,13 +33776,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -33800,13 +33797,13 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -33821,13 +33818,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -33845,10 +33842,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -33863,13 +33860,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -33905,10 +33902,10 @@
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -33926,10 +33923,10 @@
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
